--- a/dashboards/safety/asmis_template.xlsx
+++ b/dashboards/safety/asmis_template.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS1"/>
+  <dimension ref="A1:AW1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,6 +644,26 @@
       <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Summary</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>SUB DATE REPORTED</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Documentation</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Assigned To</t>
         </is>
       </c>
     </row>
